--- a/listini-c75s/F2_SENZA_VETRO.xlsx
+++ b/listini-c75s/F2_SENZA_VETRO.xlsx
@@ -534,55 +534,55 @@
         <v>500</v>
       </c>
       <c r="B3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N3" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A3)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A3)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -591,55 +591,55 @@
         <v>600</v>
       </c>
       <c r="B4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N4" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A4)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A4)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -648,55 +648,55 @@
         <v>700</v>
       </c>
       <c r="B5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N5" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A5)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A5)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -705,55 +705,55 @@
         <v>800</v>
       </c>
       <c r="B6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N6" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A6)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A6)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -762,55 +762,55 @@
         <v>900</v>
       </c>
       <c r="B7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N7" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A7)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A7)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -819,55 +819,55 @@
         <v>1000</v>
       </c>
       <c r="B8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N8" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A8)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A8)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -876,55 +876,55 @@
         <v>1100</v>
       </c>
       <c r="B9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N9" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A9)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A9)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -933,55 +933,55 @@
         <v>1200</v>
       </c>
       <c r="B10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N10" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A10)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A10)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -990,55 +990,55 @@
         <v>1300</v>
       </c>
       <c r="B11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N11" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A11)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A11)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1047,55 +1047,55 @@
         <v>1400</v>
       </c>
       <c r="B12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N12" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A12)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A12)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A12)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A12)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A12)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1104,55 +1104,55 @@
         <v>1500</v>
       </c>
       <c r="B13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N13" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A13)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A13)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A13)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A13)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A13)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1161,55 +1161,55 @@
         <v>1600</v>
       </c>
       <c r="B14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N14" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A14)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A14)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A14)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A14)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A14)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1218,55 +1218,55 @@
         <v>1700</v>
       </c>
       <c r="B15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N15" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A15)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A15)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A15)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A15)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A15)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1275,55 +1275,55 @@
         <v>1800</v>
       </c>
       <c r="B16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N16" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A16)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A16)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1332,55 +1332,55 @@
         <v>1900</v>
       </c>
       <c r="B17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N17" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A17)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A17)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1389,55 +1389,55 @@
         <v>2000</v>
       </c>
       <c r="B18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="J18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="K18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="L18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="M18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="N18" s="4">
-        <f>ROUND(ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A18)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A18)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)*(1+Parametri!$B$6),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$2+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$2+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$2+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -1499,55 +1499,55 @@
         <v>500</v>
       </c>
       <c r="B23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N23" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A23)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A23)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1556,55 +1556,55 @@
         <v>600</v>
       </c>
       <c r="B24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N24" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A24)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A24)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1613,55 +1613,55 @@
         <v>700</v>
       </c>
       <c r="B25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N25" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A25)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A25)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A25)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A25)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A25)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1670,55 +1670,55 @@
         <v>800</v>
       </c>
       <c r="B26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N26" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A26)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A26)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A26)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A26)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A26)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1727,55 +1727,55 @@
         <v>900</v>
       </c>
       <c r="B27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N27" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A27)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A27)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A27)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A27)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A27)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1784,55 +1784,55 @@
         <v>1000</v>
       </c>
       <c r="B28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N28" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A28)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A28)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A28)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A28)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A28)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1841,55 +1841,55 @@
         <v>1100</v>
       </c>
       <c r="B29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N29" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A29)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A29)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A29)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A29)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A29)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1898,55 +1898,55 @@
         <v>1200</v>
       </c>
       <c r="B30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N30" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A30)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A30)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A30)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A30)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A30)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1955,55 +1955,55 @@
         <v>1300</v>
       </c>
       <c r="B31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N31" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A31)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A31)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A31)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A31)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A31)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -2012,55 +2012,55 @@
         <v>1400</v>
       </c>
       <c r="B32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N32" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A32)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A32)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A32)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A32)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A32)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -2069,55 +2069,55 @@
         <v>1500</v>
       </c>
       <c r="B33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N33" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A33)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A33)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A33)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A33)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A33)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -2126,55 +2126,55 @@
         <v>1600</v>
       </c>
       <c r="B34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N34" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A34)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A34)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A34)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A34)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A34)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -2183,55 +2183,55 @@
         <v>1700</v>
       </c>
       <c r="B35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N35" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A35)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A35)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A35)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A35)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A35)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -2240,55 +2240,55 @@
         <v>1800</v>
       </c>
       <c r="B36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N36" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A36)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A36)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A36)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A36)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A36)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -2297,55 +2297,55 @@
         <v>1900</v>
       </c>
       <c r="B37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N37" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A37)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A37)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A37)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A37)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A37)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -2354,55 +2354,55 @@
         <v>2000</v>
       </c>
       <c r="B38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="J38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*J$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*J$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*J$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="K38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*K$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*K$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*K$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="L38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*L$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*L$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*L$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="M38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*M$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*M$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*M$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="N38" s="4">
-        <f>ROUND(((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A38)*Parametri!$B$1*(1-Parametri!$B$2)+((Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A38)+Coefficienti!$B$7)*(1-Parametri!$B$3))*(1+Parametri!$B$4)+Ferramenta!$D$14+Coefficienti!$B$8*Parametri!$B$5,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*N$22+Coefficienti!$B$3*$A38)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*N$22+Coefficienti!$B$6*$A38)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*N$22+Coefficienti!$B$9*$A38)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$14+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -2417,84 +2417,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Prezzo profili €/kg (10820 CAT.B +ADD — RAL 7016)</t>
+          <t>Prezzo profili taglio termico €/kg (33320 CAT.B +ADD — RAL 7016)</t>
         </is>
       </c>
       <c r="B1" s="6" t="n">
-        <v>14.82</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Sconto profili su listino AluK</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n">
-        <v>0.43</v>
+          <t>Prezzo profili normali €/kg (10820 CAT.B +ADD — fermavetri, aggiuntivi, gocciolatoio)</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>14.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Sconto accessori/guarnizioni su listino AluK</t>
+          <t>Sconto profili su listino AluK C75S/C82S-CS</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Sfrido</t>
+          <t>Sconto accessori/guarnizioni su listino AluK</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Tariffa oraria manodopera €/h</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>65</v>
+          <t>Sfrido</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Tariffa oraria manodopera €/h</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>Ricarico su costo totale</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B7" s="7" t="n">
         <v>2.13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Celle gialle = valori modificabili: tutte le griglie si ricalcolano.</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Listino AluK decorrenza 15-06-2026. Ferramenta: prezzi nel foglio dedicato.</t>
+          <t>Celle gialle = valori modificabili: tutte le griglie si ricalcolano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Prezzi: listino AluK C75S/C82S-CS decorrenza 2026-06-15 (listini-db). Ferramenta: prezzi nel foglio dedicato.</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2518,122 +2528,159 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Peso alluminio costante (kg)</t>
+          <t>Peso profili taglio termico costante (kg)</t>
         </is>
       </c>
       <c r="B1" s="5" t="n">
-        <v>-0.81311</v>
+        <v>-0.36516</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Peso per mm di L (kg/mm)</t>
+          <t>Peso taglio termico per mm di L (kg/mm)</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0.00672</v>
+        <v>0.00598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Peso per mm di H (kg/mm)</t>
+          <t>Peso taglio termico per mm di H (kg/mm)</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.01087</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Guarnizioni costante (€ listino)</t>
+          <t>Peso profili normali costante (kg)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.015277</v>
+        <v>-0.44795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Guarnizioni per mm di L (€/mm)</t>
+          <t>Peso normali per mm di L (kg/mm)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.002453</v>
+        <v>0.00074</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Guarnizioni per mm di H (€/mm)</t>
+          <t>Peso normali per mm di H (kg/mm)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.003157</v>
+        <v>0.00187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Accessori totale (€ listino)</t>
+          <t>Guarnizioni costante (€ listino)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>54.91</v>
+        <v>0.015277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ore manodopera</t>
+          <t>Guarnizioni per mm di L (€/mm)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4.33333333</v>
+        <v>0.002453</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Guarnizioni per mm di H (€/mm)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0.003157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Derivati dalle distinte catalogo AluK C75S sez. 8 e pesi kg/m catalogo v3.</t>
-        </is>
+          <t>Accessori totale (€ listino)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>54.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Assunzioni: supporti vetro V62008 = 4 per vetro; mascherine V51015 = 2 pz;</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>fermavetro battenti N45860 (0,37 kg/m), fisso coppia N45856 (0,62 kg/m);</t>
-        </is>
+          <t>Ore manodopera</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4.33333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>squadrette V40022/V40037 prezzate come V40022 (0,607 €).</t>
+          <t>Derivati dalle distinte catalogo AluK C75S sez. 8 e pesi kg/m catalogo v3.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Manodopera: 1h telaio + 1h/anta + 20' ferramenta/anta + 20'/vetro.</t>
+          <t>Assunzioni: supporti vetro V62008 = 4 per vetro; mascherine V51015 = 2 pz;</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Prezzi unitari accessori e guarnizioni dal listino AluK 15-06-2026 (pre-sconto).</t>
+          <t>fermavetro battenti N45860 (0,37 kg/m), fisso coppia N45856 (0,62 kg/m);</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>squadrette V40022/V40037 prezzate come V40022 (0,607 €).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Manodopera: 1h telaio + 1h/anta + 20' ferramenta/anta + 20'/vetro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Taglio termico = codici B (stipite, anta, battuta centrale, soglia); normali = N/K (aggiuntivo, gocciolatoio, fermavetri).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Prezzi unitari accessori e guarnizioni (pre-sconto): listino AluK C75S/C82S-CS decorrenza 2026-06-15 (listini-db).</t>
         </is>
       </c>
     </row>
